--- a/测试登录参数化.xlsx
+++ b/测试登录参数化.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555"/>
+    <workbookView windowWidth="21600" windowHeight="9105"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,19 +42,19 @@
     <t>acc返回断言</t>
   </si>
   <si>
-    <t>账号错误</t>
+    <t>PC号超长-账号错误</t>
   </si>
   <si>
     <t>顾客编号格式不正确(Invalid PC ID)</t>
   </si>
   <si>
-    <t>密码正确</t>
+    <t>正常登录-密码正确</t>
   </si>
   <si>
     <t>何思宇 (60003152)</t>
   </si>
   <si>
-    <t>密码错误</t>
+    <t>登录失败-密码为空</t>
   </si>
   <si>
     <t>密码不能为空 (Password is missing)</t>
@@ -1229,7 +1229,8 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="3" width="13.5486725663717" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1592920353982" style="1" customWidth="1"/>
+    <col min="2" max="3" width="13.5486725663717" style="1" customWidth="1"/>
     <col min="4" max="4" width="29.8761061946903" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9.02654867256637" style="1"/>
   </cols>
@@ -1283,9 +1284,7 @@
       <c r="B4" s="1">
         <v>60003152</v>
       </c>
-      <c r="C4" s="1">
-        <v>1232</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
         <v>9</v>
       </c>

--- a/测试登录参数化.xlsx
+++ b/测试登录参数化.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9105"/>
+    <workbookView windowWidth="21600" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>场景</t>
   </si>
@@ -39,25 +39,40 @@
     <t>password</t>
   </si>
   <si>
-    <t>acc返回断言</t>
-  </si>
-  <si>
-    <t>PC号超长-账号错误</t>
+    <t>预期结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 前置操作（可选）</t>
+  </si>
+  <si>
+    <t>顾客编号格式不正确</t>
   </si>
   <si>
     <t>顾客编号格式不正确(Invalid PC ID)</t>
   </si>
   <si>
+    <t>无</t>
+  </si>
+  <si>
     <t>正常登录-密码正确</t>
   </si>
   <si>
-    <t>何思宇 (60003152)</t>
-  </si>
-  <si>
-    <t>登录失败-密码为空</t>
+    <t>返回官网</t>
+  </si>
+  <si>
+    <t>密码为空</t>
   </si>
   <si>
     <t>密码不能为空 (Password is missing)</t>
+  </si>
+  <si>
+    <t>清空密码</t>
+  </si>
+  <si>
+    <t>密码错误</t>
+  </si>
+  <si>
+    <t>用户名/密码错误</t>
   </si>
   <si>
     <t>acc</t>
@@ -1226,16 +1241,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="27.1592920353982" style="1" customWidth="1"/>
     <col min="2" max="3" width="13.5486725663717" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.8761061946903" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.02654867256637" style="1"/>
+    <col min="4" max="4" width="48.6637168141593" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.9734513274336" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.02654867256637" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1248,10 +1264,13 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>7398479374</v>
@@ -1260,12 +1279,15 @@
         <v>234</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1">
         <v>60003152</v>
@@ -1274,19 +1296,41 @@
         <v>123</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
         <v>60003152</v>
       </c>
-      <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1">
+        <v>60003152</v>
+      </c>
+      <c r="C5" s="1">
+        <v>231231</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1316,12 +1360,12 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1">
         <v>60003156</v>

--- a/测试登录参数化.xlsx
+++ b/测试登录参数化.xlsx
@@ -1247,7 +1247,7 @@
     <col min="1" max="1" width="27.1592920353982" style="1" customWidth="1"/>
     <col min="2" max="3" width="13.5486725663717" style="1" customWidth="1"/>
     <col min="4" max="4" width="48.6637168141593" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.9734513274336" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.3274336283186" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9.02654867256637" style="1"/>
   </cols>
   <sheetData>
